--- a/output/pdf_financials_xlsx/SNA.xlsx
+++ b/output/pdf_financials_xlsx/SNA.xlsx
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.047564</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.152942</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.047564</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.152942</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0</v>
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.550092</v>
+        <v>0.502528</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.380852</v>
+        <v>0.22791</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.122327</v>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">

--- a/output/pdf_financials_xlsx/SNA.xlsx
+++ b/output/pdf_financials_xlsx/SNA.xlsx
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.106065</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.106064</v>
       </c>
     </row>
     <row r="29">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.823661</v>
+        <v>-5.717596</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-5.823661</v>
+        <v>-5.717597</v>
       </c>
     </row>
     <row r="30">
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-4561.138001253133</v>
+        <v>-4478.067042606516</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-7797.944618515841</v>
+        <v>-7655.923783508744</v>
       </c>
     </row>
     <row r="31">
@@ -2073,13 +2073,13 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.106065</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.106065</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.106064</v>
       </c>
     </row>
     <row r="101">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="B120" s="3" t="n">
-        <v>0</v>
+        <v>4.1793</v>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>0.893925</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -3761,7 +3761,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>0.106065</v>
       </c>
@@ -4243,7 +4247,11 @@
           <t>Issuance of shares, net of issuance costs</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E52" s="5" t="n">
         <v>4.1793</v>
       </c>

--- a/output/pdf_financials_xlsx/SNA.xlsx
+++ b/output/pdf_financials_xlsx/SNA.xlsx
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.086546</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PurchaseOfIntangibles</t>
+          <t>NetIntangiblesPurchaseAndSale</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
